--- a/prix/diessner.xlsx
+++ b/prix/diessner.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1C691D-60BC-41C6-A45F-A62003C10201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CB0A56-0BA5-431F-803C-B8D1E0F88727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23124" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -742,7 +742,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -762,7 +762,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -782,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -802,7 +802,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="14">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -842,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="F7" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -876,13 +876,13 @@
         <v>68</v>
       </c>
       <c r="D9" s="13">
-        <v>16.47</v>
+        <v>17.37</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>58</v>
@@ -906,7 +906,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -938,13 +938,13 @@
         <v>67</v>
       </c>
       <c r="D12" s="13">
-        <v>31.3</v>
+        <v>33.549999999999997</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>57</v>
@@ -968,7 +968,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1000,13 +1000,13 @@
         <v>66</v>
       </c>
       <c r="D15" s="13">
-        <v>58.53</v>
+        <v>63.03</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>61</v>
@@ -1062,13 +1062,13 @@
         <v>68</v>
       </c>
       <c r="D18" s="13">
-        <v>20.150000000000002</v>
+        <v>21.05</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>58</v>
@@ -1088,13 +1088,13 @@
         <v>67</v>
       </c>
       <c r="D19" s="13">
-        <v>35.950000000000003</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="14">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>57</v>
@@ -1114,13 +1114,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="13">
-        <v>61.300000000000004</v>
+        <v>65.8</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>64</v>
@@ -1146,7 +1146,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="16">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1160,13 +1160,13 @@
         <v>65</v>
       </c>
       <c r="D22" s="15">
-        <v>230.96</v>
+        <v>242.21</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>62</v>
@@ -1192,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="F23" s="16">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1206,13 +1206,13 @@
         <v>66</v>
       </c>
       <c r="D24" s="15">
-        <v>92.49</v>
+        <v>96.99</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>61</v>
